--- a/users.xlsx
+++ b/users.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carvalho\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72CA9279-8D04-4A4A-857F-D8EDB9AE69E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B8A7A77-9538-482E-86E5-92356D3A8782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34935" yWindow="375" windowWidth="38700" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2910" yWindow="2910" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="50">
   <si>
     <t>email</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>HEI_OFC_LPH3_ENE-00.xlsx</t>
+  </si>
+  <si>
+    <t>daniel.torakai@wernersobek.com</t>
   </si>
 </sst>
 </file>
@@ -412,8 +415,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -424,7 +427,7 @@
     <col min="7" max="7" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" ht="13.9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -525,7 +528,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28">
+    <row r="6" spans="1:7" ht="27">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -585,7 +588,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28">
+    <row r="9" spans="1:7" ht="27">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -605,7 +608,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28">
+    <row r="10" spans="1:7" ht="27">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -774,6 +777,20 @@
       </c>
       <c r="E19" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2">
+        <v>73050</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -781,13 +798,14 @@
     <mergeCell ref="E1:F1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="D2:D16 D20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"edit mode,viewer mode"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A20" r:id="rId3" xr:uid="{DF021492-4BC5-4814-A749-90B8C38B0860}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
